--- a/output/pdf_financials_xlsx/BLR.X.xlsx
+++ b/output/pdf_financials_xlsx/BLR.X.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.09432</v>
+        <v>5.963959</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.243191</v>
+        <v>1.718385</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.5379119999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.256553</v>
       </c>
     </row>
     <row r="11">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.044154</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001056</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.272483</v>
+        <v>-10.316637</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-21.06607</v>
+        <v>-21.067126</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.667077</v>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.272483</v>
+        <v>-10.316637</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-21.06607</v>
+        <v>-21.067126</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.667077</v>
@@ -1085,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000364</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000364</v>
       </c>
     </row>
     <row r="35">
@@ -1123,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000364</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000364</v>
       </c>
     </row>
     <row r="37">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5480,20 +5480,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>-5.963959</v>
+        <v>5.963959</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-1.718385</v>
+        <v>1.718385</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.5379119999999999</v>
+        <v>0.5379119999999999</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>-0.256553</v>
+        <v>0.256553</v>
       </c>
     </row>
     <row r="68">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
